--- a/Documentazione/Progetto DHARP - DHarp 2.0 - BOM.xlsx
+++ b/Documentazione/Progetto DHARP - DHarp 2.0 - BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS - IN PROGRESS\Progetto DHARP\Documentazione\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D074D25A-5618-42CE-8E72-AF08B026645C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CEF853-2B85-4956-96FA-3F6E9AF108BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5520" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <author>tc={A548CBB1-CADB-44A3-B7E5-193D259A46E5}</author>
   </authors>
   <commentList>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{A548CBB1-CADB-44A3-B7E5-193D259A46E5}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{A548CBB1-CADB-44A3-B7E5-193D259A46E5}">
       <text>
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="94">
   <si>
     <t>CODICE</t>
   </si>
@@ -122,9 +122,6 @@
     <t>Tappi per i profilati in alluminio quadrati</t>
   </si>
   <si>
-    <t>Tappi per i profilati in alluminio rettangilari</t>
-  </si>
-  <si>
     <t>CAVACC0.3</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
     <t>Ferro zincato</t>
   </si>
   <si>
-    <t>Piastrina asolata ad angolo a L spessore 2mm</t>
-  </si>
-  <si>
     <t>Rivetti diametro 3,2 mm per spessori 2 - 4 mm</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>SCAALUAA23,5x23,5x1000x1,5</t>
   </si>
   <si>
-    <t>Costruzione della struttura</t>
-  </si>
-  <si>
     <t>Filamento elettrico dell'arpa (circa 22 m)</t>
   </si>
   <si>
@@ -276,6 +267,78 @@
   </si>
   <si>
     <t>Per unire tutte le componenti della struttura</t>
+  </si>
+  <si>
+    <t>RUNCCI-YUN</t>
+  </si>
+  <si>
+    <t>Connettori a banana da 4 mm femmina</t>
+  </si>
+  <si>
+    <t>BANF4MM</t>
+  </si>
+  <si>
+    <t>R841</t>
+  </si>
+  <si>
+    <t>Connessione con le 2 linee di filamento</t>
+  </si>
+  <si>
+    <t>Costruzione della struttura del telaio</t>
+  </si>
+  <si>
+    <t>Tappi per i profilati in alluminio rettangolari</t>
+  </si>
+  <si>
+    <t>Tappi per impermealizzazione dei profilati di sezione quadrata</t>
+  </si>
+  <si>
+    <t>Tappi per impermealizzazione dei profilati di sezione rettangolare</t>
+  </si>
+  <si>
+    <t>75 x 75 x 20 x 2 mm</t>
+  </si>
+  <si>
+    <t>Hettich</t>
+  </si>
+  <si>
+    <t>Piastrina angolare sinistra</t>
+  </si>
+  <si>
+    <t>Piastrina angolare destra</t>
+  </si>
+  <si>
+    <t>ANGOL60x45x16x1.5</t>
+  </si>
+  <si>
+    <t>ANGOR60x45x16x1.5</t>
+  </si>
+  <si>
+    <t>60 x 45 x 16 x 1,5 mm</t>
+  </si>
+  <si>
+    <t>Acciaio galvanizzato</t>
+  </si>
+  <si>
+    <t>Self - Bricofer</t>
+  </si>
+  <si>
+    <t>MASIDEF</t>
+  </si>
+  <si>
+    <t>ELLEFER80x80x20x2</t>
+  </si>
+  <si>
+    <t>Piastrina asolata ad angolo ad L lunga</t>
+  </si>
+  <si>
+    <t>Piastrina asolata ad angolo ad L corta</t>
+  </si>
+  <si>
+    <t>Per unire gli scatolati in alluminio</t>
+  </si>
+  <si>
+    <t>Per fissare la piattina inferiore di plastica</t>
   </si>
 </sst>
 </file>
@@ -465,7 +528,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -750,12 +813,114 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -764,9 +929,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -776,9 +938,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -791,18 +950,6 @@
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -868,9 +1015,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -889,9 +1033,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -919,9 +1060,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -943,9 +1081,6 @@
     <xf numFmtId="164" fontId="8" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -958,13 +1093,7 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -976,9 +1105,6 @@
     <xf numFmtId="1" fontId="5" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -993,6 +1119,87 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1289,7 +1496,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F7" dT="2024-10-31T14:49:14.98" personId="{9DC2B2FD-C7E5-4F12-9462-41247DF8639A}" id="{A548CBB1-CADB-44A3-B7E5-193D259A46E5}">
+  <threadedComment ref="F8" dT="2024-10-31T14:49:14.98" personId="{9DC2B2FD-C7E5-4F12-9462-41247DF8639A}" id="{A548CBB1-CADB-44A3-B7E5-193D259A46E5}">
     <text>Percentuale del totale</text>
   </threadedComment>
 </ThreadedComments>
@@ -1300,7 +1507,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="B1:H15"/>
+  <dimension ref="B1:H18"/>
   <sheetFormatPr defaultColWidth="3.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" customWidth="1"/>
@@ -1316,15 +1523,15 @@
     <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:8" ht="24.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="68">
-        <f xml:space="preserve"> SUM( G6:G14 )</f>
-        <v>57.957599999999999</v>
+      <c r="G2" s="58">
+        <f xml:space="preserve"> SUM( G6:G17 )</f>
+        <v>75.256599999999978</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1353,204 +1560,313 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="50">
         <v>21690</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="18">
+      <c r="E6" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="12">
         <v>1</v>
       </c>
-      <c r="G6" s="66">
+      <c r="G6" s="56">
         <f xml:space="preserve"> F6 * 'Materiale plastico'!G3</f>
         <v>4.2</v>
       </c>
-      <c r="H6" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="60" t="s">
+      <c r="H6" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="85">
+        <v>2</v>
+      </c>
+      <c r="G7" s="86">
+        <f xml:space="preserve"> F7 * 'Materiale elettrico'!F3</f>
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="H7" s="87" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="21">
+      <c r="D8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="15">
         <f xml:space="preserve"> (100 * 22) / 300</f>
         <v>7.333333333333333</v>
       </c>
-      <c r="G7" s="67">
-        <f xml:space="preserve"> (F7 / 100) * 'Materiale elettrico'!F3</f>
+      <c r="G8" s="57">
+        <f xml:space="preserve"> (F8 / 100) * 'Materiale elettrico'!F4</f>
         <v>1.1726000000000001</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="H8" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="69" t="s">
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F9" s="5">
         <v>2</v>
       </c>
-      <c r="G8" s="66">
-        <f xml:space="preserve"> F8 * 'Materiale plastico'!G5</f>
+      <c r="G9" s="56">
+        <f xml:space="preserve"> F9 * 'Materiale plastico'!G5</f>
         <v>4.4950000000000001</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="69" t="s">
+      <c r="H9" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="E10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="5">
         <v>4</v>
       </c>
-      <c r="G9" s="66">
-        <f xml:space="preserve"> F9 * 'Materiale plastico'!G6</f>
+      <c r="G10" s="56">
+        <f xml:space="preserve"> F10 * 'Materiale plastico'!G6</f>
         <v>8.99</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="58" t="s">
+      <c r="H10" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D11" s="4">
         <v>25170</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="E11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="5">
         <v>3</v>
       </c>
-      <c r="G10" s="66">
-        <f xml:space="preserve"> F10 * 'Scatolati in alluminio'!G6</f>
+      <c r="G11" s="56">
+        <f xml:space="preserve"> F11 * 'Scatolati in alluminio'!G6</f>
         <v>29.849999999999998</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="58" t="s">
+      <c r="H11" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D12" s="4">
         <v>25326</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="E12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="5">
         <v>1</v>
       </c>
-      <c r="G11" s="66">
-        <f xml:space="preserve"> F11 * 'Scatolati in alluminio'!G4</f>
+      <c r="G12" s="56">
+        <f xml:space="preserve"> F12 * 'Scatolati in alluminio'!G4</f>
         <v>9.25</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="58" t="s">
+      <c r="H12" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="66">
-        <f xml:space="preserve"> F12 * Ferramenta!G4</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="11"/>
-    </row>
-    <row r="15" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="D13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="5">
+        <v>60</v>
+      </c>
+      <c r="G13" s="56">
+        <f xml:space="preserve"> F13 * Ferramenta!G7</f>
+        <v>7.6920000000000002</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="4">
+        <v>9100629</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="56">
+        <f xml:space="preserve"> F14 * Ferramenta!G4</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="4">
+        <v>9100630</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="56">
+        <f xml:space="preserve"> F15 * Ferramenta!G3</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="4">
+        <v>9105893</v>
+      </c>
+      <c r="E16" s="92" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="93">
+        <v>4</v>
+      </c>
+      <c r="G16" s="86">
+        <f xml:space="preserve"> F16 * Ferramenta!G6</f>
+        <v>2.25</v>
+      </c>
+      <c r="H16" s="94" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="95" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="7">
+        <v>9105896</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="8">
+        <v>6</v>
+      </c>
+      <c r="G17" s="67">
+        <f xml:space="preserve"> F17 * Ferramenta!G5</f>
+        <v>4.4250000000000007</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{116C45D7-173F-4EC9-B192-C1FA585F59C3}"/>
-    <hyperlink ref="B7" r:id="rId2" xr:uid="{1A70E09A-167E-4C9F-9F90-B20932A61F06}"/>
-    <hyperlink ref="B8" r:id="rId3" xr:uid="{B5598FD8-4C3F-4C99-A5F8-C821B17C83C5}"/>
-    <hyperlink ref="B9" r:id="rId4" xr:uid="{A5119098-79F0-4A5A-A0A6-747DA98737A4}"/>
-    <hyperlink ref="B11" r:id="rId5" xr:uid="{266BC76A-EFB5-47F6-9DC9-986E489A702E}"/>
-    <hyperlink ref="B10" r:id="rId6" xr:uid="{C279A041-0827-4487-ACC2-73B759AFFDC4}"/>
-    <hyperlink ref="B12" r:id="rId7" xr:uid="{B89F72D3-AD5B-4B62-91E6-3537B7C60922}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{1A70E09A-167E-4C9F-9F90-B20932A61F06}"/>
+    <hyperlink ref="B9" r:id="rId3" xr:uid="{B5598FD8-4C3F-4C99-A5F8-C821B17C83C5}"/>
+    <hyperlink ref="B10" r:id="rId4" xr:uid="{A5119098-79F0-4A5A-A0A6-747DA98737A4}"/>
+    <hyperlink ref="B12" r:id="rId5" xr:uid="{266BC76A-EFB5-47F6-9DC9-986E489A702E}"/>
+    <hyperlink ref="B11" r:id="rId6" xr:uid="{C279A041-0827-4487-ACC2-73B759AFFDC4}"/>
+    <hyperlink ref="B13" r:id="rId7" xr:uid="{B89F72D3-AD5B-4B62-91E6-3537B7C60922}"/>
+    <hyperlink ref="B7" r:id="rId8" xr:uid="{BA108BF4-2C54-45FA-A6B7-792BF5427762}"/>
+    <hyperlink ref="B14" r:id="rId9" xr:uid="{C3188214-D27F-4129-BD4B-9F3129CD0CBA}"/>
+    <hyperlink ref="B15" r:id="rId10" xr:uid="{A2EF5679-7E89-45B8-8BA4-6CABA9CCD125}"/>
+    <hyperlink ref="B16" r:id="rId11" xr:uid="{ED506DBC-340E-4151-944A-1A567EA8961A}"/>
+    <hyperlink ref="B17" r:id="rId12" location="additional" xr:uid="{DA0C1F28-194E-4C2A-824D-239447A63408}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
-  <legacyDrawing r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <legacyDrawing r:id="rId14"/>
 </worksheet>
 </file>
 
@@ -1559,12 +1875,12 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="51.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.88671875" bestFit="1" customWidth="1"/>
@@ -1578,82 +1894,122 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:12" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="12" t="s">
+      <c r="G2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="79" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="79" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="80">
+        <f xml:space="preserve"> (H3 + I3) / G3</f>
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="G3" s="81">
+        <v>30</v>
+      </c>
+      <c r="H3" s="80">
+        <v>10.98</v>
+      </c>
+      <c r="I3" s="80">
+        <v>0</v>
+      </c>
+      <c r="J3" s="79" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="82">
+        <v>46114</v>
+      </c>
+      <c r="L3" s="83"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D4" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="65">
-        <f xml:space="preserve"> (H3 + I3) / G3</f>
+      <c r="F4" s="74">
+        <f xml:space="preserve"> (H4 + I4) / G4</f>
         <v>15.99</v>
       </c>
-      <c r="G3" s="76">
+      <c r="G4" s="75">
         <v>1</v>
       </c>
-      <c r="H3" s="65">
+      <c r="H4" s="74">
         <v>15.99</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="13" t="s">
+      <c r="I4" s="74">
+        <v>0</v>
+      </c>
+      <c r="J4" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K4" s="76">
         <v>46113</v>
       </c>
-      <c r="L3" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="L4" s="77"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{D5D85210-D258-42FC-8784-D738E5B32BE1}"/>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{D5D85210-D258-42FC-8784-D738E5B32BE1}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{1591671C-BCB0-444B-9D33-B98529041B0C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1681,40 +2037,40 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="36" t="s">
+      <c r="E2" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="36" t="s">
+      <c r="G2" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" s="36" t="s">
+      <c r="H2" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="37" t="s">
+      <c r="M2" s="31" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1722,218 +2078,238 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="26">
         <v>21690</v>
       </c>
-      <c r="E3" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="61">
+      <c r="E3" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="52">
         <f t="shared" ref="G3:G7" si="0" xml:space="preserve"> (I3 + J3) / H3</f>
         <v>4.2</v>
       </c>
-      <c r="H3" s="73">
+      <c r="H3" s="61">
         <v>1</v>
       </c>
-      <c r="I3" s="64">
+      <c r="I3" s="55">
         <v>4.2</v>
       </c>
-      <c r="J3" s="64"/>
-      <c r="K3" s="31" t="s">
+      <c r="J3" s="55">
+        <v>0</v>
+      </c>
+      <c r="K3" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="33">
+      <c r="L3" s="27">
         <v>45584</v>
       </c>
-      <c r="M3" s="34" t="s">
-        <v>67</v>
+      <c r="M3" s="28" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="31" t="s">
+      <c r="B4" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="62">
+      <c r="D4" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="73">
+      <c r="H4" s="61">
         <v>1</v>
       </c>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="31" t="s">
+      <c r="I4" s="55"/>
+      <c r="J4" s="55">
+        <v>0</v>
+      </c>
+      <c r="K4" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="33"/>
-      <c r="M4" s="34" t="s">
-        <v>66</v>
+      <c r="L4" s="27"/>
+      <c r="M4" s="28" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="24" t="s">
+      <c r="B5" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="62">
+      <c r="F5" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="53">
         <f t="shared" si="0"/>
         <v>2.2475000000000001</v>
       </c>
-      <c r="H5" s="74">
+      <c r="H5" s="62">
         <v>4</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="53">
         <v>8.99</v>
       </c>
-      <c r="J5" s="62"/>
-      <c r="K5" s="23" t="s">
+      <c r="J5" s="53">
+        <v>0</v>
+      </c>
+      <c r="K5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="19">
         <v>46113</v>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="20" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="24" t="s">
+      <c r="B6" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="62">
+      <c r="F6" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="53">
         <f t="shared" si="0"/>
         <v>2.2475000000000001</v>
       </c>
-      <c r="H6" s="74">
+      <c r="H6" s="62">
         <v>4</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="53">
         <v>8.99</v>
       </c>
-      <c r="J6" s="62"/>
-      <c r="K6" s="23" t="s">
+      <c r="J6" s="53">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="19">
         <v>46113</v>
       </c>
-      <c r="M6" s="26"/>
+      <c r="M6" s="20" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="D7" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="62">
+      <c r="F7" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="74">
+      <c r="H7" s="62">
         <v>2</v>
       </c>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="25">
+      <c r="I7" s="53"/>
+      <c r="J7" s="53">
+        <v>0</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="19">
         <v>46111</v>
       </c>
-      <c r="M7" s="26"/>
+      <c r="M7" s="20" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="28" t="s">
+      <c r="B8" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="63">
+      <c r="F8" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="54">
         <f xml:space="preserve"> (I8 + J8) / H8</f>
         <v>2.2475000000000001</v>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="63">
         <v>4</v>
       </c>
-      <c r="I8" s="63">
+      <c r="I8" s="54">
         <v>8.99</v>
       </c>
-      <c r="J8" s="63"/>
-      <c r="K8" s="27" t="s">
+      <c r="J8" s="54">
+        <v>0</v>
+      </c>
+      <c r="K8" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="23">
         <v>46113</v>
       </c>
-      <c r="M8" s="30"/>
+      <c r="M8" s="24" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -1958,60 +2334,60 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="44" t="s">
+      <c r="E2" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="44" t="s">
+      <c r="G2" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" s="44" t="s">
+      <c r="H2" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="45" t="s">
+      <c r="M2" s="38" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2019,89 +2395,223 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="77">
+      <c r="B3" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="34">
+        <v>9100630</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="64">
         <f xml:space="preserve"> I3 / H3</f>
-        <v>0.75</v>
-      </c>
-      <c r="H3" s="51">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H3" s="43">
         <v>1</v>
       </c>
-      <c r="I3" s="77">
-        <v>0.75</v>
-      </c>
-      <c r="J3" s="77"/>
-      <c r="K3" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="53">
-        <v>45564</v>
-      </c>
-      <c r="M3" s="54" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I3" s="64">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J3" s="64">
+        <v>0</v>
+      </c>
+      <c r="K3" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="45">
+        <v>45964</v>
+      </c>
+      <c r="M3" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="34">
+        <v>9100629</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="64">
+        <f xml:space="preserve"> I4 / H4</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H4" s="43">
+        <v>1</v>
+      </c>
+      <c r="I4" s="64">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J4" s="64">
+        <v>0</v>
+      </c>
+      <c r="K4" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4" s="89">
+        <v>45964</v>
+      </c>
+      <c r="M4" s="90" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="91" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="34">
+        <v>9105896</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="64">
+        <f xml:space="preserve"> I5 / H5</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="H5" s="43">
+        <v>4</v>
+      </c>
+      <c r="I5" s="64">
+        <v>2.95</v>
+      </c>
+      <c r="J5" s="64">
+        <v>0</v>
+      </c>
+      <c r="K5" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="60">
+        <v>46114</v>
+      </c>
+      <c r="M5" s="88" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="34">
+        <v>9105893</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="64">
+        <f xml:space="preserve"> I6 / H6</f>
+        <v>0.5625</v>
+      </c>
+      <c r="H6" s="43">
+        <v>4</v>
+      </c>
+      <c r="I6" s="64">
+        <v>2.25</v>
+      </c>
+      <c r="J6" s="64">
+        <v>0</v>
+      </c>
+      <c r="K6" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="60">
+        <v>46114</v>
+      </c>
+      <c r="M6" s="88" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="39" t="s">
+      <c r="D7" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="78">
-        <f xml:space="preserve"> I4 / H4</f>
+      <c r="G7" s="65">
+        <f xml:space="preserve"> I7 / H7</f>
         <v>0.12820000000000001</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H7" s="44">
         <v>50</v>
       </c>
-      <c r="I4" s="78">
+      <c r="I7" s="65">
         <v>6.41</v>
       </c>
-      <c r="J4" s="78"/>
-      <c r="K4" s="39" t="s">
+      <c r="J7" s="65">
+        <v>0</v>
+      </c>
+      <c r="K7" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="55">
+      <c r="L7" s="47">
         <v>46113</v>
       </c>
-      <c r="M4" s="56" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="M7" s="48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{6D5AF8AE-1870-4793-BFFE-FA81415867FF}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{6D5AF8AE-1870-4793-BFFE-FA81415867FF}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{9E222B36-CFBF-4F59-BE32-5E985F856435}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{F03B53B4-FDB8-40B3-B970-B5CC6038C6B3}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{ADA52809-E174-460C-824E-A82332C98DAD}"/>
+    <hyperlink ref="B5" r:id="rId5" location="additional" xr:uid="{90F0D3EF-572F-439A-8564-9F51B00A2DD2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -2130,203 +2640,213 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="44" t="s">
+      <c r="E2" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="81" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="44" t="s">
+      <c r="G2" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" s="44" t="s">
+      <c r="H2" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="45" t="s">
+      <c r="M2" s="38" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="79">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="70" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="66">
         <f xml:space="preserve"> I3 / H3</f>
         <v>9.25</v>
       </c>
-      <c r="H3" s="51">
+      <c r="H3" s="43">
         <v>1</v>
       </c>
-      <c r="I3" s="79">
+      <c r="I3" s="66">
         <v>9.25</v>
       </c>
-      <c r="J3" s="77"/>
-      <c r="K3" s="38" t="s">
+      <c r="J3" s="64">
+        <v>0</v>
+      </c>
+      <c r="K3" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="71">
+      <c r="L3" s="60">
         <v>45520</v>
       </c>
-      <c r="M3" s="72"/>
+      <c r="M3" s="71"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="46" t="s">
+      <c r="B4" s="69"/>
+      <c r="C4" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="39">
         <v>25326</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="79">
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="66">
         <f xml:space="preserve"> I4 / H4</f>
         <v>9.25</v>
       </c>
-      <c r="H4" s="51">
+      <c r="H4" s="43">
         <v>1</v>
       </c>
-      <c r="I4" s="79">
+      <c r="I4" s="66">
         <v>9.25</v>
       </c>
-      <c r="J4" s="77"/>
-      <c r="K4" s="38" t="s">
+      <c r="J4" s="64">
+        <v>0</v>
+      </c>
+      <c r="K4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="71">
+      <c r="L4" s="60">
         <v>45564</v>
       </c>
-      <c r="M4" s="72"/>
+      <c r="M4" s="71"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="79">
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="70" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="66">
         <f t="shared" ref="G5:G7" si="0" xml:space="preserve"> I5 / H5</f>
         <v>9.9499999999999993</v>
       </c>
-      <c r="H5" s="51">
+      <c r="H5" s="43">
         <v>1</v>
       </c>
-      <c r="I5" s="79">
+      <c r="I5" s="66">
         <v>9.9499999999999993</v>
       </c>
-      <c r="J5" s="77"/>
-      <c r="K5" s="38" t="s">
+      <c r="J5" s="64">
+        <v>0</v>
+      </c>
+      <c r="K5" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="71">
+      <c r="L5" s="60">
         <v>45520</v>
       </c>
-      <c r="M5" s="72"/>
+      <c r="M5" s="71"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="46" t="s">
+      <c r="B6" s="69"/>
+      <c r="C6" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="39">
         <v>25170</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="79">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="66">
         <f t="shared" si="0"/>
         <v>9.9499999999999993</v>
       </c>
-      <c r="H6" s="51">
+      <c r="H6" s="43">
         <v>1</v>
       </c>
-      <c r="I6" s="79">
+      <c r="I6" s="66">
         <v>9.9499999999999993</v>
       </c>
-      <c r="J6" s="77"/>
-      <c r="K6" s="38" t="s">
+      <c r="J6" s="64">
+        <v>0</v>
+      </c>
+      <c r="K6" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="71">
+      <c r="L6" s="60">
         <v>45564</v>
       </c>
-      <c r="M6" s="72"/>
+      <c r="M6" s="71"/>
     </row>
     <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="39" t="s">
+      <c r="B7" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="33">
         <v>25171</v>
       </c>
-      <c r="E7" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="78">
+      <c r="E7" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="65">
         <f t="shared" si="0"/>
         <v>11.859</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="44">
         <v>1</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="65">
         <v>11.859</v>
       </c>
-      <c r="J7" s="78"/>
-      <c r="K7" s="39" t="s">
+      <c r="J7" s="65">
+        <v>0</v>
+      </c>
+      <c r="K7" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="55">
+      <c r="L7" s="47">
         <v>45520</v>
       </c>
-      <c r="M7" s="56"/>
+      <c r="M7" s="48"/>
     </row>
     <row r="8" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>

--- a/Documentazione/Progetto DHARP - DHarp 2.0 - BOM.xlsx
+++ b/Documentazione/Progetto DHARP - DHarp 2.0 - BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS - IN PROGRESS\Progetto DHARP\Documentazione\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmasili\Documents\GitHub\DHarp\Documentazione\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CEF853-2B85-4956-96FA-3F6E9AF108BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9DFB67-19F2-4FCB-B0C5-25D0E2A64339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5520" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="12" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Scatolati in alluminio" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="103">
   <si>
     <t>CODICE</t>
   </si>
@@ -137,15 +138,9 @@
     <t>MATERIALE</t>
   </si>
   <si>
-    <t>ELLEFER40x40x20X2</t>
-  </si>
-  <si>
     <t>40 x 40 x 20 x 2 mm</t>
   </si>
   <si>
-    <t>Ferro zincato</t>
-  </si>
-  <si>
     <t>Rivetti diametro 3,2 mm per spessori 2 - 4 mm</t>
   </si>
   <si>
@@ -296,9 +291,6 @@
     <t>Tappi per impermealizzazione dei profilati di sezione rettangolare</t>
   </si>
   <si>
-    <t>75 x 75 x 20 x 2 mm</t>
-  </si>
-  <si>
     <t>Hettich</t>
   </si>
   <si>
@@ -326,9 +318,6 @@
     <t>MASIDEF</t>
   </si>
   <si>
-    <t>ELLEFER80x80x20x2</t>
-  </si>
-  <si>
     <t>Piastrina asolata ad angolo ad L lunga</t>
   </si>
   <si>
@@ -339,6 +328,45 @@
   </si>
   <si>
     <t>Per fissare la piattina inferiore di plastica</t>
+  </si>
+  <si>
+    <t>Per sorreggere la vaschetta in retina</t>
+  </si>
+  <si>
+    <t>DESCRIZIONE</t>
+  </si>
+  <si>
+    <t>80 x 80 x 20 x 2 mm</t>
+  </si>
+  <si>
+    <t>DY2006776</t>
+  </si>
+  <si>
+    <t>ELLEFER50x50x20X2</t>
+  </si>
+  <si>
+    <t>ELLEFER100x100x20x2</t>
+  </si>
+  <si>
+    <t>DY2006779</t>
+  </si>
+  <si>
+    <t>Acciaio Inox A2 - AISI 304, resistente a ruggine e corrosione</t>
+  </si>
+  <si>
+    <t>Piastrina dritta forata</t>
+  </si>
+  <si>
+    <t>Acciaio zincato bianco</t>
+  </si>
+  <si>
+    <t>PIASTRA200x20x2</t>
+  </si>
+  <si>
+    <t>DY200101MZ</t>
+  </si>
+  <si>
+    <t>200 x 20 x 2 mm</t>
   </si>
 </sst>
 </file>
@@ -528,7 +556,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -915,12 +943,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1120,15 +1159,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1199,6 +1229,34 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1523,7 +1581,7 @@
     <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:8" ht="24.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
@@ -1547,7 +1605,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
@@ -1556,12 +1614,12 @@
         <v>2</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B6" s="49" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>18</v>
@@ -1570,7 +1628,7 @@
         <v>21690</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F6" s="12">
         <v>1</v>
@@ -1580,31 +1638,31 @@
         <v>4.2</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="81" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="84" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="84" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="84" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="85">
+      <c r="F7" s="82">
         <v>2</v>
       </c>
-      <c r="G7" s="86">
+      <c r="G7" s="83">
         <f xml:space="preserve"> F7 * 'Materiale elettrico'!F3</f>
         <v>0.73199999999999998</v>
       </c>
-      <c r="H7" s="87" t="s">
-        <v>46</v>
+      <c r="H7" s="84" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1618,7 +1676,7 @@
         <v>24</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F8" s="15">
         <f xml:space="preserve"> (100 * 22) / 300</f>
@@ -1629,15 +1687,15 @@
         <v>1.1726000000000001</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="49" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" s="59" t="s">
         <v>16</v>
@@ -1653,21 +1711,21 @@
         <v>4.4950000000000001</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="49" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="59" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F10" s="5">
         <v>4</v>
@@ -1677,7 +1735,7 @@
         <v>8.99</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
@@ -1691,7 +1749,7 @@
         <v>25170</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F11" s="5">
         <v>3</v>
@@ -1701,7 +1759,7 @@
         <v>29.849999999999998</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
@@ -1715,7 +1773,7 @@
         <v>25326</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F12" s="5">
         <v>1</v>
@@ -1725,45 +1783,45 @@
         <v>9.25</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F13" s="5">
         <v>60</v>
       </c>
       <c r="G13" s="56">
-        <f xml:space="preserve"> F13 * Ferramenta!G7</f>
+        <f xml:space="preserve"> F13 * Ferramenta!G8</f>
         <v>7.6920000000000002</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="49" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D14" s="4">
         <v>9100629</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F14" s="5">
         <v>1</v>
@@ -1773,21 +1831,21 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="49" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D15" s="4">
         <v>9100630</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F15" s="5">
         <v>1</v>
@@ -1797,45 +1855,45 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="49" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="4">
-        <v>9105893</v>
-      </c>
-      <c r="E16" s="92" t="s">
-        <v>92</v>
-      </c>
-      <c r="F16" s="93">
+      <c r="F16" s="90">
         <v>4</v>
       </c>
-      <c r="G16" s="86">
+      <c r="G16" s="83">
         <f xml:space="preserve"> F16 * Ferramenta!G6</f>
         <v>2.25</v>
       </c>
-      <c r="H16" s="94" t="s">
-        <v>45</v>
+      <c r="H16" s="91" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="95" t="s">
-        <v>89</v>
+      <c r="B17" s="92" t="s">
+        <v>95</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="7">
-        <v>9105896</v>
+        <v>85</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F17" s="8">
         <v>6</v>
@@ -1845,7 +1903,7 @@
         <v>4.4250000000000007</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1862,7 +1920,7 @@
     <hyperlink ref="B14" r:id="rId9" xr:uid="{C3188214-D27F-4129-BD4B-9F3129CD0CBA}"/>
     <hyperlink ref="B15" r:id="rId10" xr:uid="{A2EF5679-7E89-45B8-8BA4-6CABA9CCD125}"/>
     <hyperlink ref="B16" r:id="rId11" xr:uid="{ED506DBC-340E-4151-944A-1A567EA8961A}"/>
-    <hyperlink ref="B17" r:id="rId12" location="additional" xr:uid="{DA0C1F28-194E-4C2A-824D-239447A63408}"/>
+    <hyperlink ref="B17" r:id="rId12" xr:uid="{DA0C1F28-194E-4C2A-824D-239447A63408}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
@@ -1907,16 +1965,16 @@
         <v>5</v>
       </c>
       <c r="F2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>3</v>
@@ -1932,75 +1990,75 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="78" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="79" t="s">
+      <c r="B3" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="79" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="79" t="s">
+      <c r="C3" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="80">
+      <c r="E3" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="77">
         <f xml:space="preserve"> (H3 + I3) / G3</f>
         <v>0.36599999999999999</v>
       </c>
-      <c r="G3" s="81">
+      <c r="G3" s="78">
         <v>30</v>
       </c>
-      <c r="H3" s="80">
+      <c r="H3" s="77">
         <v>10.98</v>
       </c>
-      <c r="I3" s="80">
+      <c r="I3" s="77">
         <v>0</v>
       </c>
-      <c r="J3" s="79" t="s">
+      <c r="J3" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="82">
+      <c r="K3" s="79">
         <v>46114</v>
       </c>
-      <c r="L3" s="83"/>
+      <c r="L3" s="80"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C4" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="73" t="s">
+      <c r="D4" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="73" t="s">
+      <c r="E4" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="74">
+      <c r="F4" s="71">
         <f xml:space="preserve"> (H4 + I4) / G4</f>
         <v>15.99</v>
       </c>
-      <c r="G4" s="75">
+      <c r="G4" s="72">
         <v>1</v>
       </c>
-      <c r="H4" s="74">
+      <c r="H4" s="71">
         <v>15.99</v>
       </c>
-      <c r="I4" s="74">
+      <c r="I4" s="71">
         <v>0</v>
       </c>
-      <c r="J4" s="73" t="s">
+      <c r="J4" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="76">
+      <c r="K4" s="73">
         <v>46113</v>
       </c>
-      <c r="L4" s="77"/>
+      <c r="L4" s="74"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2053,16 +2111,16 @@
         <v>1</v>
       </c>
       <c r="G2" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="30" t="s">
         <v>47</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>49</v>
       </c>
       <c r="K2" s="30" t="s">
         <v>3</v>
@@ -2079,7 +2137,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>18</v>
@@ -2088,10 +2146,10 @@
         <v>21690</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G3" s="52">
         <f t="shared" ref="G3:G7" si="0" xml:space="preserve"> (I3 + J3) / H3</f>
@@ -2113,24 +2171,24 @@
         <v>45584</v>
       </c>
       <c r="M3" s="28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G4" s="53">
         <f t="shared" si="0"/>
@@ -2148,7 +2206,7 @@
       </c>
       <c r="L4" s="27"/>
       <c r="M4" s="28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -2156,10 +2214,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>16</v>
@@ -2168,7 +2226,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G5" s="53">
         <f t="shared" si="0"/>
@@ -2190,7 +2248,7 @@
         <v>46113</v>
       </c>
       <c r="M5" s="20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -2198,10 +2256,10 @@
         <v>10</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>16</v>
@@ -2210,7 +2268,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G6" s="53">
         <f t="shared" si="0"/>
@@ -2232,24 +2290,24 @@
         <v>46113</v>
       </c>
       <c r="M6" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G7" s="53">
         <f t="shared" si="0"/>
@@ -2263,21 +2321,21 @@
         <v>0</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L7" s="19">
         <v>46111</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>16</v>
@@ -2286,7 +2344,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G8" s="54">
         <f xml:space="preserve"> (I8 + J8) / H8</f>
@@ -2308,7 +2366,7 @@
         <v>46113</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2334,14 +2392,14 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37.6640625" bestFit="1" customWidth="1"/>
@@ -2370,16 +2428,16 @@
         <v>1</v>
       </c>
       <c r="G2" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="37" t="s">
         <v>47</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>49</v>
       </c>
       <c r="K2" s="37" t="s">
         <v>3</v>
@@ -2388,27 +2446,27 @@
         <v>9</v>
       </c>
       <c r="M2" s="38" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="91" t="s">
-        <v>84</v>
+      <c r="B3" s="88" t="s">
+        <v>81</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D3" s="34">
         <v>9100630</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G3" s="64">
         <f xml:space="preserve"> I3 / H3</f>
@@ -2424,33 +2482,33 @@
         <v>0</v>
       </c>
       <c r="K3" s="35" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L3" s="45">
         <v>45964</v>
       </c>
       <c r="M3" s="46" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="91" t="s">
-        <v>83</v>
+      <c r="B4" s="88" t="s">
+        <v>80</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D4" s="34">
         <v>9100629</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G4" s="64">
         <f xml:space="preserve"> I4 / H4</f>
@@ -2466,33 +2524,33 @@
         <v>0</v>
       </c>
       <c r="K4" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="L4" s="89">
+        <v>84</v>
+      </c>
+      <c r="L4" s="86">
         <v>45964</v>
       </c>
-      <c r="M4" s="90" t="s">
-        <v>81</v>
+      <c r="M4" s="87" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="91" t="s">
-        <v>89</v>
+      <c r="B5" s="88" t="s">
+        <v>95</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="34">
-        <v>9105896</v>
+        <v>85</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>96</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G5" s="64">
         <f xml:space="preserve"> I5 / H5</f>
@@ -2508,33 +2566,33 @@
         <v>0</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L5" s="60">
         <v>46114</v>
       </c>
-      <c r="M5" s="88" t="s">
-        <v>90</v>
+      <c r="M5" s="85" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="88" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="34" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="34">
-        <v>9105893</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>27</v>
       </c>
       <c r="G6" s="64">
         <f xml:space="preserve"> I6 / H6</f>
@@ -2550,65 +2608,100 @@
         <v>0</v>
       </c>
       <c r="K6" s="35" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L6" s="60">
         <v>46114</v>
       </c>
-      <c r="M6" s="88" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M6" s="85" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="97" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="97" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="97" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="98"/>
+      <c r="H7" s="99">
+        <v>1</v>
+      </c>
+      <c r="I7" s="98"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="101">
+        <v>46122</v>
+      </c>
+      <c r="M7" s="102" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="33" t="s">
+      <c r="D8" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="65">
-        <f xml:space="preserve"> I7 / H7</f>
+      <c r="G8" s="65">
+        <f xml:space="preserve"> I8 / H8</f>
         <v>0.12820000000000001</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H8" s="44">
         <v>50</v>
       </c>
-      <c r="I7" s="65">
+      <c r="I8" s="65">
         <v>6.41</v>
       </c>
-      <c r="J7" s="65">
+      <c r="J8" s="65">
         <v>0</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="K8" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="47">
+      <c r="L8" s="47">
         <v>46113</v>
       </c>
-      <c r="M7" s="48" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="M8" s="48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{6D5AF8AE-1870-4793-BFFE-FA81415867FF}"/>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{6D5AF8AE-1870-4793-BFFE-FA81415867FF}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{9E222B36-CFBF-4F59-BE32-5E985F856435}"/>
     <hyperlink ref="B3" r:id="rId3" xr:uid="{F03B53B4-FDB8-40B3-B970-B5CC6038C6B3}"/>
     <hyperlink ref="B6" r:id="rId4" xr:uid="{ADA52809-E174-460C-824E-A82332C98DAD}"/>
-    <hyperlink ref="B5" r:id="rId5" location="additional" xr:uid="{90F0D3EF-572F-439A-8564-9F51B00A2DD2}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{90F0D3EF-572F-439A-8564-9F51B00A2DD2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
@@ -2656,16 +2749,16 @@
         <v>1</v>
       </c>
       <c r="G2" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="37" t="s">
         <v>47</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>49</v>
       </c>
       <c r="K2" s="37" t="s">
         <v>3</v>
@@ -2678,16 +2771,16 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="93" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="39"/>
       <c r="D3" s="39"/>
-      <c r="E3" s="70" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="70" t="s">
+      <c r="E3" s="94" t="s">
         <v>65</v>
+      </c>
+      <c r="F3" s="94" t="s">
+        <v>63</v>
       </c>
       <c r="G3" s="66">
         <f xml:space="preserve"> I3 / H3</f>
@@ -2708,21 +2801,21 @@
       <c r="L3" s="60">
         <v>45520</v>
       </c>
-      <c r="M3" s="71"/>
+      <c r="M3" s="95"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="69"/>
+      <c r="B4" s="93"/>
       <c r="C4" s="39" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="39">
         <v>25326</v>
       </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
       <c r="G4" s="66">
         <f xml:space="preserve"> I4 / H4</f>
         <v>9.25</v>
@@ -2742,19 +2835,19 @@
       <c r="L4" s="60">
         <v>45564</v>
       </c>
-      <c r="M4" s="71"/>
+      <c r="M4" s="95"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="93" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="39"/>
       <c r="D5" s="39"/>
-      <c r="E5" s="70" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="70" t="s">
-        <v>66</v>
+      <c r="E5" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="94" t="s">
+        <v>64</v>
       </c>
       <c r="G5" s="66">
         <f t="shared" ref="G5:G7" si="0" xml:space="preserve"> I5 / H5</f>
@@ -2775,21 +2868,21 @@
       <c r="L5" s="60">
         <v>45520</v>
       </c>
-      <c r="M5" s="71"/>
+      <c r="M5" s="95"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="69"/>
+      <c r="B6" s="93"/>
       <c r="C6" s="39" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="39">
         <v>25170</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
       <c r="G6" s="66">
         <f t="shared" si="0"/>
         <v>9.9499999999999993</v>
@@ -2809,11 +2902,11 @@
       <c r="L6" s="60">
         <v>45564</v>
       </c>
-      <c r="M6" s="71"/>
+      <c r="M6" s="95"/>
     </row>
     <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>18</v>
@@ -2822,10 +2915,10 @@
         <v>25171</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G7" s="65">
         <f t="shared" si="0"/>
